--- a/icb-contacts.xlsx
+++ b/icb-contacts.xlsx
@@ -532,7 +532,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://bsw.icb.nhs.uk/about-us/freedom-of-information/</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TODO — added 4 May 2026 during schema migration; press email not yet researched.; Forwarded to South Central and West CSU for processing</t>
+          <t>TODO — added 4 May 2026 during schema migration; press email not yet researched.; Forwarded to South Central and West CSU for processing | press source URL set 2026-06-20 (was a placeholder); address confirmed unchanged</t>
         </is>
       </c>
     </row>
@@ -1265,23 +1265,27 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.midandsouthessex.ics.nhs.uk/contact/</t>
+          <t>https://www.essex.icb.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>eicb.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>mseicb-foi@nhs.net</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.midandsouthessex.ics.nhs.uk/contact/foi/</t>
+          <t>https://www.essex.icb.nhs.uk/contact/foi/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>New merged entity from 1 April 2026; predecessor Mid and South Essex address still active.; input website seed was mid and south Essex ICB</t>
+          <t>New merged entity from 1 April 2026; predecessor Mid and South Essex address still active.; input website seed was mid and south Essex ICB | 2026-06-20: org migrated to essex.icb.nhs.uk (old midandsouthessex.ics.nhs.uk 301-redirects); FOI updated to eicb.foi@nhs.net (prior mseicb-foi@nhs.net moved to alt); new media page is form-only so the old press address may be defunct - manual check needed</t>
         </is>
       </c>
     </row>

--- a/icb-contacts.xlsx
+++ b/icb-contacts.xlsx
@@ -423,7 +423,7 @@
     <col width="57" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
@@ -795,10 +795,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>nnicb-nn.dln-communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>ddicb.communications@nhs.net</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>https://joinedupcarederbyshire.co.uk/contact-us/staff-and-media-contacting-us/</t>
@@ -815,7 +819,11 @@
           <t>https://joinedupcarederbyshire.co.uk/derbyshire-integrated-care-board/freedom-of-information/</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>press primary updated 2026-06-27 from joinedupcarederbyshire.co.uk media/comms section; prior value ddicb.communications@nhs.net moved to press_email_alt</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -847,10 +855,14 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://devon.icb.nhs.uk/freedom-of-information/</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>https://onedevon.org.uk/nhs-devon/freedom-of-information/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>foi_source_url updated 2026-06-27 (old devon.icb.nhs.uk path now 404); FOI email D-CCG.FOI@nhs.net unchanged</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">

--- a/icb-contacts.xlsx
+++ b/icb-contacts.xlsx
@@ -719,7 +719,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Temp/Comms contacts.xlsx (May 2026)</t>
+          <t>https://cios.icb.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">

--- a/icb-contacts.xlsx
+++ b/icb-contacts.xlsx
@@ -1470,10 +1470,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>nnicb-nn.dln-communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>nnicb-nn.comms@nhs.net</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>https://notts.icb.nhs.uk/contact-us/general-enquiries/</t>
@@ -1492,7 +1496,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Live page returning 504 gateway timeout; email confirmed via Wayback Machine archive (Jan 2026 capture)</t>
+          <t>Live page returning 504 gateway timeout; email confirmed via Wayback Machine archive (Jan 2026 capture) | press primary updated 2026-07-18 from https://notts.icb.nhs.uk/contact-us/general-enquiries/ (page now lists nnicb-nn.dln-communications@nhs.net for media/press); prior value nnicb-nn.comms@nhs.net moved to _alt</t>
         </is>
       </c>
     </row>

--- a/icb-contacts.xlsx
+++ b/icb-contacts.xlsx
@@ -1314,10 +1314,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>nsicb.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>nwicb.communications@nhs.net</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>https://www.norfolkandsuffolk.icb.nhs.uk/contact/</t>
@@ -1325,10 +1329,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>nsicb.foi@nhs.net</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>nwicb.foi@nhs.net</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>https://www.norfolkandsuffolk.icb.nhs.uk/about/governance/foi/</t>
@@ -1336,7 +1344,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Email obfuscated via Cloudflare; decoded from data-cfemail (legacy Norfolk and Waveney prefix)</t>
+          <t>Email obfuscated via Cloudflare; decoded from data-cfemail (legacy Norfolk and Waveney prefix) primary updated 2026-07-30 from https://www.norfolkandsuffolk.icb.nhs.uk/contact/ and https://www.norfolkandsuffolk.icb.nhs.uk/about/governance/foi/ (cfemail-decoded); prior nwicb.* values moved to _alt.</t>
         </is>
       </c>
     </row>

--- a/icb-contacts.xlsx
+++ b/icb-contacts.xlsx
@@ -423,7 +423,7 @@
     <col width="57" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
@@ -650,10 +650,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>blmkicb.contactus@nhs.net</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>foi@centraleast.nhs.uk</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>https://www.centraleast.icb.nhs.uk/about/requests/foi/</t>
@@ -661,7 +665,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>New merged entity from 1 April 2026 (BLMK + Cambs &amp; Peterborough + Herts &amp; West Essex). Use BLMK predecessor address for now per Dave May 2026 â€” new ICB site offers only a contact form.</t>
+          <t>New merged entity from 1 April 2026 (BLMK + Cambs &amp; Peterborough + Herts &amp; West Essex). Use BLMK predecessor address for now per Dave May 2026 â€” new ICB site offers only a contact form. [2026-08-01] foi_email primary updated 2026-08-01 from https://www.centraleast.icb.nhs.uk/about/requests/foi/ — the FOI-team address on that page is Cloudflare-obfuscated and decodes to blmkicb.contactus@nhs.net; the previous primary foi@centraleast.nhs.uk no longer appears anywhere on the page and moved to _alt.</t>
         </is>
       </c>
     </row>
@@ -1068,13 +1072,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>hnyicb.press@nhs.net</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>hnyicb.communications@nhs.net</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://humberandnorthyorkshire.icb.nhs.uk/contact-us/</t>
+          <t>https://humberandnorthyorkshire.icb.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1088,7 +1096,11 @@
           <t>https://humberandnorthyorkshire.icb.nhs.uk/foi</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>[2026-08-01] press_email primary updated 2026-08-01 from https://humberandnorthyorkshire.icb.nhs.uk/contact/; prior value hnyicb.communications@nhs.net moved to _alt. The old /contact-us/ page now 404s, so press_source_url was repointed to /contact/.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1228,33 +1240,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>nnicb-nn.comms@nhs.net</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>LICB.office@nhs.net</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>charley.blyth@nhs.net</t>
-        </is>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://lincolnshire.icb.nhs.uk/contact-us/</t>
+          <t>https://lincolnshire.icb.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>nnicb-nn.dln.fois@nhs.net</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>agem.lincolnshireicb.foi@nhs.net</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://lincolnshire.icb.nhs.uk/freedom-of-information</t>
+          <t>https://lincolnshire.icb.nhs.uk/contact/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>General office address â€” no published press-specific email.</t>
+          <t>General office address â€” no published press-specific email. [2026-08-01] press_email and foi_email primaries updated 2026-08-01 from https://lincolnshire.icb.nhs.uk/contact/, which now publishes a press-specific address (nnicb-nn.comms@nhs.net) and routes FOI to nnicb-nn.dln.fois@nhs.net; prior primaries LICB.office@nhs.net and agem.lincolnshireicb.foi@nhs.net moved to _alt (the previous press _alt charley.blyth@nhs.net, a personal address, is no longer published). Both old source URLs (/contact-us/ and /freedom-of-information) now 404.</t>
         </is>
       </c>
     </row>
@@ -1747,13 +1763,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>sxicb.surreyandsussex.media@nhs.net</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>sxicb.comms@nhs.net</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.sussex.ics.nhs.uk/contact-us/</t>
+          <t>https://www.surreysussex.icb.nhs.uk/contact-us/</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1769,7 +1789,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Legacy Sussex ICB address â€” new Surrey and Sussex site has form only. Likely still routed correctly.; Input seed was Sussex ICS website; Surrey may have separate contact</t>
+          <t>Legacy Sussex ICB address â€” new Surrey and Sussex site has form only. Likely still routed correctly.; Input seed was Sussex ICS website; Surrey may have separate contact [2026-08-01] press_email primary updated 2026-08-01 from https://www.surreysussex.icb.nhs.uk/contact-us/; prior value sxicb.comms@nhs.net moved to _alt. The ICB moved to the surreysussex.icb.nhs.uk domain on 1 April 2026 and states the old sussex.ics.nhs.uk site is no longer updated and will be archived — FOI is still only published on the old site (sxicb.foi@nhs.net, unchanged), so foi_source_url is left pointing there for now and should be revisited once the new site publishes an FOI page.</t>
         </is>
       </c>
     </row>

--- a/icb-contacts.xlsx
+++ b/icb-contacts.xlsx
@@ -604,10 +604,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Bbcs.communications@nhs.net</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>comms.blackcountry@nhs.net</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>https://blackcountry.icb.nhs.uk/contact-us</t>
@@ -624,7 +628,11 @@
           <t>https://blackcountry.icb.nhs.uk/legal-info</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>primary updated 2026-08-15 from [https://blackcountry.icb.nhs.uk/contact-us]; prior value moved to _alt.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/icb-contacts.xlsx
+++ b/icb-contacts.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TODO — added 4 May 2026 during schema migration; press email not yet researched.; Forwarded to South Central and West CSU for processing | press source URL set 2026-06-20 (was a placeholder); address confirmed unchanged</t>
+          <t>TODO — added 4 May 2026 during schema migration; press email not yet researched.; Forwarded to South Central and West CSU for processing | press source URL set 2026-06-20 (was a placeholder); address confirmed unchanged | 2026-08-22: bswicb.media@nhs.net and bswicb.foi@nhs.net both re-confirmed on the freedom-of-information page (which carries the media address too).</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>New merged entity from 1 April 2026; predecessor Mid and South Essex address still active.; input website seed was mid and south Essex ICB | 2026-06-20: org migrated to essex.icb.nhs.uk (old midandsouthessex.ics.nhs.uk 301-redirects); FOI updated to eicb.foi@nhs.net (prior mseicb-foi@nhs.net moved to alt); new media page is form-only so the old press address may be defunct - manual check needed</t>
+          <t>New merged entity from 1 April 2026; predecessor Mid and South Essex address still active.; input website seed was mid and south Essex ICB | 2026-06-20: org migrated to essex.icb.nhs.uk (old midandsouthessex.ics.nhs.uk 301-redirects); FOI updated to eicb.foi@nhs.net (prior mseicb-foi@nhs.net moved to alt); new media page is form-only so the old press address may be defunct - manual check needed | 2026-08-22: /contact/press-media/ is still contact-form only with no address published, so communications@midandsouthessex.ics.nhs.uk remains unverified and may be defunct - manual check still outstanding. FOI address Eicb.foi@nhs.net re-confirmed by decoding the cfemail token on /contact/foi/.</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,11 @@
           <t>https://www.shropshiretelfordandwrekin.nhs.uk/contact-us/</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-08-22: stw.communications@nhs.net and stw.ssot.foi@nhs.net both re-confirmed on /contact-us/.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
